--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource Observation pour définir une Glycémie
+    <t>Profil biologie de la ressource Observation pour définir une Glycémie
 Ce profil permet de gérer 4 types d'indicateurs de glycémie:
 - le taux de glucose sanguin, mesuré en mg/dl
 - le taux de glucose interstitiel, mesuré en mg/dl

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -524,7 +524,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -567,7 +567,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1020,7 +1020,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1049,7 +1049,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1324,7 +1324,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1652,7 +1652,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1717,7 +1717,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1773,7 +1773,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1815,7 +1815,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1924,7 +1924,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1974,7 +1974,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -2007,7 +2007,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2044,7 +2044,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2066,7 +2066,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2131,7 +2131,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -7354,7 +7354,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>337</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>358</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>364</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>370</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>375</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>384</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>408</v>
       </c>
@@ -10850,7 +10850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>435</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>464</v>
       </c>
@@ -12178,7 +12178,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>518</v>
       </c>
@@ -13988,7 +13988,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>568</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>585</v>
       </c>
@@ -15788,7 +15788,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>660</v>
       </c>
@@ -16270,7 +16270,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>670</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>678</v>
       </c>
@@ -16514,7 +16514,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>687</v>
       </c>
@@ -16882,12 +16882,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP119">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$120</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4581" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4619" uniqueCount="701">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,10 +85,9 @@
   </si>
   <si>
     <t>Profil biologie de la ressource Observation pour définir une Glycémie
-Ce profil permet de gérer 4 types d'indicateurs de glycémie:
+Ce profil permet de gérer 3 types d'indicateurs de glycémie:
 - le taux de glucose sanguin, mesuré en mg/dl
 - le taux de glucose interstitiel, mesuré en mg/dl
-- l’hémoglobine glyquée (Hb1Ac) mesurée en %
 - l’index de gestion de glycémie (IGG) qui procure une estimation de l’HbA1c également mesuré en %
 L'extension MesNumberOfDays permet de spécifier le nombre de jours dans la mesure du taux de glucose interstitiel et de l’index de gestion de glycémie (IGG) .
 L'extension MesMomentOfMeasurement (contexte de la mesure) est utilisée dans le cas de la mesure du glucose sanguin.</t>
@@ -446,7 +445,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -650,7 +649,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -666,11 +665,28 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre.</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -1223,7 +1239,6 @@
     <t>Types de glycémie:
 • Glucose sanguin
 • Glucose interstitiel
-• Hémoglobine glyquée (HbA1c)
 • Index de gestion de glycémie (IGG)</t>
   </si>
   <si>
@@ -1442,7 +1457,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2510,7 +2525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP119"/>
+  <dimension ref="A1:AP120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="64.81640625" customWidth="true" bestFit="true"/>
@@ -2523,7 +2538,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4872,7 +4887,7 @@
         <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4958,12 +4973,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4984,13 +5001,13 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5041,19 +5058,19 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -5065,7 +5082,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5076,10 +5093,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5090,7 +5107,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -5102,13 +5119,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5147,31 +5164,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -5183,7 +5200,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5194,10 +5211,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5205,10 +5222,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -5220,24 +5237,22 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>82</v>
@@ -5267,31 +5282,31 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>121</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5303,7 +5318,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5314,10 +5329,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5325,7 +5340,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
@@ -5340,22 +5355,24 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>82</v>
@@ -5373,11 +5390,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5395,10 +5414,10 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>93</v>
@@ -5407,7 +5426,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5430,10 +5449,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5456,13 +5475,13 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5489,13 +5508,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5513,7 +5530,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5525,7 +5542,7 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5537,7 +5554,7 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5548,21 +5565,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5574,17 +5591,15 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5621,31 +5636,31 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5668,21 +5683,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5691,23 +5706,21 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5743,19 +5756,19 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5767,7 +5780,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5776,10 +5789,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5790,10 +5803,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5813,19 +5826,23 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5873,19 +5890,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5894,10 +5911,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5908,21 +5925,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5934,17 +5951,15 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5981,31 +5996,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6028,21 +6043,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -6051,23 +6066,21 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6103,31 +6116,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6136,10 +6149,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6150,10 +6163,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6161,7 +6174,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
@@ -6176,18 +6189,20 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6235,7 +6250,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6256,10 +6271,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6270,10 +6285,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6281,7 +6296,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -6296,18 +6311,18 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6355,7 +6370,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6376,10 +6391,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6390,10 +6405,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6401,7 +6416,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
@@ -6416,17 +6431,17 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6475,7 +6490,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6496,10 +6511,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6510,10 +6525,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6536,19 +6551,17 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6597,7 +6610,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6618,10 +6631,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6632,10 +6645,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6658,19 +6671,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6719,7 +6732,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6740,10 +6753,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6754,14 +6767,12 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6779,19 +6790,23 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6839,19 +6854,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6860,10 +6875,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6877,43 +6892,41 @@
         <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D37" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>114</v>
+        <v>307</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6961,7 +6974,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6970,7 +6983,7 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>122</v>
@@ -6985,7 +6998,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -7003,7 +7016,7 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7016,23 +7029,25 @@
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7081,7 +7096,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7093,22 +7108,22 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>192</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -7116,14 +7131,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7142,17 +7157,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7201,7 +7216,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7216,19 +7231,19 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -7236,14 +7251,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7262,18 +7277,18 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7321,7 +7336,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7336,16 +7351,16 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7354,48 +7369,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>169</v>
+        <v>335</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7419,11 +7432,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7441,13 +7456,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -7456,30 +7471,30 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7490,31 +7505,31 @@
         <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7539,35 +7554,35 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7576,34 +7591,32 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7612,7 +7625,7 @@
         <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>94</v>
@@ -7624,19 +7637,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7664,28 +7677,26 @@
         <v>173</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AC43" s="2"/>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7709,35 +7720,37 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7746,16 +7759,20 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>108</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7779,13 +7796,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7803,19 +7820,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>110</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7827,10 +7844,10 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>111</v>
+        <v>361</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7838,21 +7855,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7864,17 +7881,15 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7911,31 +7926,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7956,48 +7971,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -8033,19 +8046,19 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8057,7 +8070,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8066,10 +8079,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8078,12 +8091,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8091,31 +8104,35 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8163,19 +8180,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8184,10 +8201,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8198,21 +8215,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8224,17 +8241,15 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8271,31 +8286,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8316,54 +8331,52 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8393,31 +8406,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8426,10 +8439,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8438,12 +8451,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8451,13 +8464,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8466,24 +8479,26 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8525,7 +8540,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8546,10 +8561,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8558,12 +8573,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8571,13 +8586,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8586,24 +8601,24 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8645,7 +8660,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8666,10 +8681,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8678,12 +8693,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8691,13 +8706,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8706,27 +8721,27 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8765,7 +8780,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8786,10 +8801,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8800,10 +8815,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8826,19 +8841,17 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8848,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>82</v>
@@ -8887,7 +8900,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8908,10 +8921,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8922,10 +8935,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8948,19 +8961,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9009,7 +9022,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9030,10 +9043,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9042,26 +9055,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9070,19 +9083,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>298</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>388</v>
+        <v>300</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>389</v>
+        <v>301</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9107,11 +9120,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -9129,10 +9144,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>384</v>
+        <v>302</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>93</v>
@@ -9144,62 +9159,66 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>393</v>
+        <v>303</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>394</v>
+        <v>304</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>108</v>
+        <v>391</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9223,13 +9242,11 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9247,10 +9264,10 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>110</v>
+        <v>389</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>93</v>
@@ -9259,44 +9276,44 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>111</v>
+        <v>399</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9308,17 +9325,15 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9355,31 +9370,31 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9402,14 +9417,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9425,23 +9440,21 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9477,19 +9490,19 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9501,7 +9514,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9510,10 +9523,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9524,10 +9537,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9538,7 +9551,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9547,19 +9560,23 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9607,19 +9624,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9628,10 +9645,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9642,21 +9659,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9668,17 +9685,15 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9715,31 +9730,31 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9762,21 +9777,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9785,23 +9800,21 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9837,31 +9850,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9870,10 +9883,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9884,10 +9897,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9895,7 +9908,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>93</v>
@@ -9910,18 +9923,20 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9969,7 +9984,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9990,10 +10005,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -10004,10 +10019,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10015,7 +10030,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
@@ -10030,18 +10045,18 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10089,7 +10104,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10110,10 +10125,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10124,10 +10139,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10135,7 +10150,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
@@ -10150,17 +10165,17 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10209,7 +10224,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10230,10 +10245,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10244,10 +10259,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10270,19 +10285,17 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10331,7 +10344,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10352,10 +10365,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10366,10 +10379,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10392,19 +10405,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10453,7 +10466,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10474,10 +10487,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10486,12 +10499,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10499,13 +10512,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
@@ -10514,19 +10527,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>409</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>410</v>
+        <v>298</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>411</v>
+        <v>299</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>412</v>
+        <v>300</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>413</v>
+        <v>301</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10575,7 +10588,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>408</v>
+        <v>302</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10590,30 +10603,30 @@
         <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>415</v>
+        <v>303</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>416</v>
+        <v>304</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10621,13 +10634,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10636,18 +10649,20 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10695,13 +10710,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10710,19 +10725,19 @@
         <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
@@ -10730,21 +10745,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10756,20 +10771,18 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>430</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10817,13 +10830,13 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
@@ -10832,44 +10845,44 @@
         <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -10878,19 +10891,19 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10939,7 +10952,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10948,50 +10961,50 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -11000,18 +11013,20 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>129</v>
+        <v>442</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11059,34 +11074,34 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>82</v>
@@ -11094,10 +11109,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11108,7 +11123,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11120,18 +11135,18 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L72" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>459</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11179,13 +11194,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -11194,30 +11209,30 @@
         <v>105</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="B73" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11228,10 +11243,10 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -11240,19 +11255,17 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11301,45 +11314,45 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11353,25 +11366,29 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>470</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>108</v>
+        <v>471</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11419,7 +11436,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>110</v>
+        <v>469</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11428,47 +11445,47 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>111</v>
+        <v>477</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11480,17 +11497,15 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11527,31 +11542,31 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11574,21 +11589,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11597,23 +11612,21 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>477</v>
+        <v>114</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>478</v>
+        <v>115</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>479</v>
+        <v>116</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11649,31 +11662,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>482</v>
+        <v>121</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11682,10 +11695,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>484</v>
+        <v>111</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11696,10 +11709,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11716,74 +11729,74 @@
         <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>169</v>
+        <v>482</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q77" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="R77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11804,10 +11817,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11818,10 +11831,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11838,28 +11851,30 @@
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="R78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11879,13 +11894,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11903,7 +11918,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11924,10 +11939,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11938,10 +11953,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11949,7 +11964,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>93</v>
@@ -11964,17 +11979,17 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11984,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>82</v>
@@ -12023,7 +12038,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12032,7 +12047,7 @@
         <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>105</v>
@@ -12044,10 +12059,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12058,10 +12073,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12084,19 +12099,17 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12106,7 +12119,7 @@
         <v>82</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>82</v>
@@ -12121,13 +12134,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12145,7 +12158,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12154,7 +12167,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12166,10 +12179,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12178,12 +12191,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12191,34 +12204,34 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J81" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K81" t="s" s="2">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O81" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12243,13 +12256,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12267,7 +12280,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12276,7 +12289,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12288,10 +12301,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>192</v>
+        <v>505</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12300,12 +12313,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12319,7 +12332,7 @@
         <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -12328,16 +12341,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>108</v>
+        <v>524</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12361,13 +12378,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12385,7 +12402,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>110</v>
+        <v>523</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12394,10 +12411,10 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12406,10 +12423,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>111</v>
+        <v>531</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12420,21 +12437,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12446,17 +12463,15 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12493,31 +12508,31 @@
         <v>82</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12540,14 +12555,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12563,23 +12578,21 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12615,19 +12628,19 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12639,7 +12652,7 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12648,10 +12661,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12662,10 +12675,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12676,7 +12689,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12685,19 +12698,23 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12745,19 +12762,19 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12766,10 +12783,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12780,21 +12797,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12806,17 +12823,15 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12853,31 +12868,31 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12900,21 +12915,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12923,23 +12938,21 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12975,31 +12988,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13008,10 +13021,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13022,10 +13035,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13033,7 +13046,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>93</v>
@@ -13048,18 +13061,20 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13107,7 +13122,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13128,10 +13143,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13142,10 +13157,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13153,7 +13168,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>93</v>
@@ -13168,18 +13183,18 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13227,7 +13242,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13248,10 +13263,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13262,10 +13277,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13273,7 +13288,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>93</v>
@@ -13288,17 +13303,17 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13347,7 +13362,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13368,10 +13383,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13382,10 +13397,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13408,19 +13423,17 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13469,7 +13482,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13490,10 +13503,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13504,10 +13517,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13530,19 +13543,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13591,7 +13604,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13612,10 +13625,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13626,21 +13639,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13649,22 +13662,22 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>540</v>
+        <v>298</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>541</v>
+        <v>299</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>542</v>
+        <v>300</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>543</v>
+        <v>301</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13689,13 +13702,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13713,13 +13726,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>538</v>
+        <v>302</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13731,31 +13744,31 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>547</v>
+        <v>303</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>548</v>
+        <v>304</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13774,19 +13787,19 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>551</v>
+        <v>230</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13811,13 +13824,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13835,7 +13848,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13853,27 +13866,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13884,7 +13897,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13896,18 +13909,20 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>225</v>
+        <v>556</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13931,13 +13946,13 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13955,13 +13970,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13973,27 +13988,27 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14007,7 +14022,7 @@
         <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -14016,20 +14031,18 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14053,11 +14066,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y96" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="Z96" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14075,7 +14090,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14093,27 +14108,27 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14127,7 +14142,7 @@
         <v>93</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14136,18 +14151,20 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14171,13 +14188,11 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14195,7 +14210,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14213,27 +14228,27 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AM97" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="B98" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14247,7 +14262,7 @@
         <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
@@ -14256,16 +14271,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14315,7 +14330,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14333,27 +14348,27 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AM98" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="B99" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14364,10 +14379,10 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>82</v>
@@ -14376,20 +14391,18 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14437,45 +14450,45 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>600</v>
+        <v>105</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14486,7 +14499,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14498,16 +14511,20 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>107</v>
+        <v>600</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>108</v>
+        <v>601</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14555,19 +14572,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>110</v>
+        <v>599</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14576,10 +14593,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>111</v>
+        <v>607</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14590,21 +14607,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14616,17 +14633,15 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14675,19 +14690,19 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14710,14 +14725,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>606</v>
+        <v>113</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14730,26 +14745,24 @@
         <v>82</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>607</v>
+        <v>115</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>608</v>
+        <v>116</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O102" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14797,7 +14810,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>609</v>
+        <v>121</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14821,7 +14834,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14839,26 +14852,26 @@
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>611</v>
+        <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>612</v>
@@ -14866,8 +14879,12 @@
       <c r="M103" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+      <c r="N103" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14915,19 +14932,19 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14936,10 +14953,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>616</v>
+        <v>192</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14950,10 +14967,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14976,13 +14993,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15033,7 +15050,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15042,7 +15059,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15054,10 +15071,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15068,10 +15085,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15094,20 +15111,16 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>225</v>
+        <v>616</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N105" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="O105" t="s" s="2">
-        <v>625</v>
-      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15131,13 +15144,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15155,7 +15168,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15164,7 +15177,7 @@
         <v>93</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>105</v>
@@ -15173,13 +15186,13 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>548</v>
+        <v>625</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15190,10 +15203,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15204,7 +15217,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15216,19 +15229,19 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15253,13 +15266,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15277,13 +15290,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15295,13 +15308,13 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15312,10 +15325,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15326,7 +15339,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15338,17 +15351,19 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15373,13 +15388,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>82</v>
+        <v>640</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15397,13 +15412,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15415,13 +15430,13 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>642</v>
+        <v>553</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15432,10 +15447,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15458,7 +15473,7 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>643</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>644</v>
@@ -15467,7 +15482,9 @@
         <v>645</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15515,7 +15532,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15536,10 +15553,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15550,10 +15567,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15564,7 +15581,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>82</v>
@@ -15573,10 +15590,10 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>648</v>
+        <v>107</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>649</v>
@@ -15584,9 +15601,7 @@
       <c r="M109" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="N109" t="s" s="2">
-        <v>651</v>
-      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15635,13 +15650,13 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
@@ -15656,10 +15671,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>652</v>
+        <v>620</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15670,10 +15685,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15696,16 +15711,16 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15755,7 +15770,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15776,24 +15791,24 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AN110" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>660</v>
-      </c>
       <c r="B111" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15807,7 +15822,7 @@
         <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
@@ -15816,20 +15831,18 @@
         <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>595</v>
+        <v>660</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>661</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O111" t="s" s="2">
         <v>663</v>
       </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15877,7 +15890,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15889,33 +15902,33 @@
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AK111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="AN111" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>667</v>
-      </c>
       <c r="B112" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15926,28 +15939,32 @@
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>107</v>
+        <v>600</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>108</v>
+        <v>666</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -15995,19 +16012,19 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>110</v>
+        <v>665</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16016,10 +16033,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>82</v>
+        <v>670</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>111</v>
+        <v>671</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16030,21 +16047,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>82</v>
@@ -16056,17 +16073,15 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16115,19 +16130,19 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16150,14 +16165,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>606</v>
+        <v>113</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16170,26 +16185,24 @@
         <v>82</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>607</v>
+        <v>115</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>608</v>
+        <v>116</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O114" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>82</v>
       </c>
@@ -16237,7 +16250,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>609</v>
+        <v>121</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16261,7 +16274,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16270,47 +16283,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I115" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>671</v>
+        <v>612</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>672</v>
+        <v>613</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>673</v>
+        <v>117</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>674</v>
+        <v>313</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16335,13 +16348,13 @@
         <v>82</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>675</v>
+        <v>82</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>676</v>
+        <v>82</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16359,34 +16372,34 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>670</v>
+        <v>614</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>677</v>
+        <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>394</v>
+        <v>192</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>82</v>
@@ -16394,10 +16407,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16405,7 +16418,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>93</v>
@@ -16420,19 +16433,19 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16460,10 +16473,10 @@
         <v>151</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16481,16 +16494,16 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>685</v>
+        <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>105</v>
@@ -16499,27 +16512,27 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>471</v>
+        <v>398</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>472</v>
+        <v>399</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16539,22 +16552,22 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>225</v>
+        <v>684</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>522</v>
+        <v>473</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16582,10 +16595,10 @@
         <v>151</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>523</v>
+        <v>688</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>524</v>
+        <v>689</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16603,7 +16616,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16612,7 +16625,7 @@
         <v>93</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>105</v>
@@ -16621,22 +16634,22 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>192</v>
+        <v>476</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>692</v>
       </c>
@@ -16645,17 +16658,17 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
@@ -16664,19 +16677,19 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>540</v>
+        <v>693</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>541</v>
+        <v>694</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>542</v>
+        <v>695</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16704,10 +16717,10 @@
         <v>151</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -16731,10 +16744,10 @@
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>82</v>
+        <v>696</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>105</v>
@@ -16743,31 +16756,31 @@
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>547</v>
+        <v>192</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16786,19 +16799,19 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>694</v>
+        <v>545</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>695</v>
+        <v>546</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>598</v>
+        <v>547</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>599</v>
+        <v>548</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16823,13 +16836,13 @@
         <v>82</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16847,7 +16860,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16865,23 +16878,145 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>601</v>
+        <v>552</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>602</v>
+        <v>553</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP119" t="s" s="2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP120" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP119">
+  <autoFilter ref="A1:AP120">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16891,7 +17026,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI118">
+  <conditionalFormatting sqref="A2:AI119">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,7 +683,7 @@
 </t>
   </si>
   <si>
-    <t>Origine de la donnée</t>
+    <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
   </si>
   <si>
     <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1806,7 +1806,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>How it was done</t>
+    <t>La méthode de mesure du cholestérol total est fortement conseillée pour déterminer si des résultats sont comparables et ainsi interpréter cette donnée.</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1891,7 +1891,7 @@
 </t>
   </si>
   <si>
-    <t>Provides guide for interpretation</t>
+    <t>Associer la mesure à l'intervalle de référence est fortement recommandé pour interpréter le résultat par rapport à la norme, qui peut varier selon de nombreux critères : la méthode d'analyse, l'age, le sexe, ...</t>
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
@@ -14483,7 +14483,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>599</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -14499,7 +14499,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>94</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,20 +673,21 @@
 </t>
   </si>
   <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+    <t>Observation.extension:mes-original-data</t>
+  </si>
+  <si>
+    <t>mes-original-data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-original-data}
 </t>
   </si>
   <si>
     <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
   </si>
   <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
+    <t>Extension permettant de renseigner la donnée originale. 
+Dans le cas où une conversion d'unité a été effectuée sur la valeur de la mesure, cette extension permet de conserver la valeur originale telle que mesurée par le dispositif.</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
